--- a/src/uploads/用户价格表模板.xlsx
+++ b/src/uploads/用户价格表模板.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hfpp2012/codes/task-backend/src/uploads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hfpp2012/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C58CB445-420B-2A4B-B770-5183EF9A8705}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53DBE8D2-38F7-A245-A1AF-EFCD179D0D9C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5180" yWindow="1860" windowWidth="28040" windowHeight="17440" xr2:uid="{E2B6C3D4-8653-734B-BA00-7FE94B1C3F32}"/>
   </bookViews>
@@ -27,6 +27,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
+    <t>用户邮箱</t>
+  </si>
+  <si>
     <t>国家</t>
   </si>
   <si>
@@ -36,13 +39,10 @@
     <t>服务费</t>
   </si>
   <si>
+    <t>ganweiliang@swqztech.com</t>
+  </si>
+  <si>
     <t>越南胡志明</t>
-  </si>
-  <si>
-    <t>用户</t>
-  </si>
-  <si>
-    <t>ganweiliang</t>
   </si>
 </sst>
 </file>
@@ -408,30 +408,30 @@
   <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.83203125" customWidth="1"/>
+    <col min="1" max="1" width="26.6640625" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
         <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
       </c>
       <c r="C2">
         <v>0.77</v>
@@ -442,7 +442,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="ganweiliang@swqztech.com" xr:uid="{B9710650-CBA4-8342-A0F4-1693B179532D}"/>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{B9710650-CBA4-8342-A0F4-1693B179532D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
